--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9256630448</v>
+        <v>46157.93092635608</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93092635608</v>
+        <v>46157.93169305876</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93169305876</v>
+        <v>46157.9339820586</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9339820586</v>
+        <v>46157.93715951388</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93715951388</v>
+        <v>46158.2821456647</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821456647</v>
+        <v>46158.29675990241</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675990241</v>
+        <v>46158.29812665682</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812665682</v>
+        <v>46158.33385550097</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385550097</v>
+        <v>46158.36855299029</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/37. ИП Лопакова аренда здания/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855299029</v>
+        <v>46158.37286053396</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
